--- a/data/minta_arajanlat.xlsx
+++ b/data/minta_arajanlat.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/595ecd328626fcde/csixwood program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="8_{BF28B8E6-6911-4314-842D-A6A0166F0E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08FDA5A4-FB07-493F-84B7-221B93135F84}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="8_{BF28B8E6-6911-4314-842D-A6A0166F0E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84BB67D5-75F8-4367-969E-01FBD417C8AE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{087A4F8E-2F22-482F-82DA-01AC2001CC58}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{087A4F8E-2F22-482F-82DA-01AC2001CC58}"/>
   </bookViews>
   <sheets>
     <sheet name="arajanlat" sheetId="2" r:id="rId1"/>
@@ -33,17 +33,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="24">
-  <si>
-    <t>1.</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>Árajánlat</t>
   </si>
   <si>
-    <t>Gyártó:</t>
-  </si>
-  <si>
     <t>Megrendelő:</t>
   </si>
   <si>
@@ -59,9 +53,6 @@
     <t>Lak. cím:</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>Adószám:</t>
   </si>
   <si>
@@ -95,9 +86,6 @@
     <t>balintbence800@gmail.com</t>
   </si>
   <si>
-    <t>Munkadíj:</t>
-  </si>
-  <si>
     <t>Az árak az ÁFA-t tartalmazzák. Az anyagról számlát tudok biztosítani, ha ez előre jelzésre kerül, munkadíjról még  nem.</t>
   </si>
   <si>
@@ -105,6 +93,36 @@
   </si>
   <si>
     <t>Dátum:</t>
+  </si>
+  <si>
+    <t>Tárgy:</t>
+  </si>
+  <si>
+    <t>Árajánlat adó:</t>
+  </si>
+  <si>
+    <t>Bálint Bence ev.</t>
+  </si>
+  <si>
+    <t>Sezegd, Selmeci utca 17.</t>
+  </si>
+  <si>
+    <t>91339968-1-26</t>
+  </si>
+  <si>
+    <t>Típus, Szín</t>
+  </si>
+  <si>
+    <t>Munkadíj, gépkopoás, rezsi:</t>
+  </si>
+  <si>
+    <t>Sz.</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Azonosító:</t>
   </si>
 </sst>
 </file>
@@ -114,7 +132,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0\ [$Ft-40E]_-;\-* #,##0\ [$Ft-40E]_-;_-* &quot;-&quot;??\ [$Ft-40E]_-;_-@_-"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,21 +316,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="238"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <vertAlign val="superscript"/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -689,73 +692,99 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42"/>
-    <xf numFmtId="2" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="42" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -814,6 +843,62 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>123826</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>601343</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>9526</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Kép 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1687EA60-49E9-873F-E7DA-90E3E15700A5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect t="8001"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="123826"/>
+          <a:ext cx="2277743" cy="1047750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1137,340 +1222,359 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1432CDCE-D980-42A2-8DB0-EED4DEC3C8EE}">
-  <dimension ref="A1:H28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A2:J30"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5" customWidth="1"/>
-    <col min="2" max="2" width="4" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-    <col min="4" max="4" width="22.44140625" customWidth="1"/>
-    <col min="5" max="5" width="10.44140625" customWidth="1"/>
-    <col min="6" max="6" width="3.88671875" customWidth="1"/>
-    <col min="7" max="7" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="1" max="1" width="3.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="6.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.42578125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="22.42578125" style="2" customWidth="1"/>
+    <col min="5" max="5" width="4.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" style="2" customWidth="1"/>
+    <col min="7" max="7" width="3.85546875" style="2" customWidth="1"/>
+    <col min="8" max="9" width="9.85546875" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="18" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-    </row>
-    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-    </row>
-    <row r="3" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="20" t="s">
-        <v>2</v>
-      </c>
+    <row r="2" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="27" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
+    </row>
+    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20"/>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="20"/>
+      <c r="E3" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="26"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+    </row>
+    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="24"/>
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+      <c r="D4" s="24"/>
+      <c r="E4" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29"/>
+      <c r="H4" s="29"/>
+      <c r="I4" s="29"/>
+      <c r="J4" s="22"/>
+    </row>
+    <row r="5" spans="1:10" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
+    </row>
+    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+    </row>
+    <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="21"/>
+      <c r="C7" s="21"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="21" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="22"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="14"/>
+      <c r="C8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="14"/>
+      <c r="C9" s="3">
+        <v>307698397</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
+    </row>
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="14"/>
+      <c r="C10" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G10" s="15"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G11" s="17"/>
+      <c r="H11" s="17"/>
+      <c r="I11" s="17"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="B12" s="14"/>
+      <c r="C12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+    </row>
+    <row r="14" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+    </row>
+    <row r="15" spans="1:10" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H16" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="7" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H17" s="6"/>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+    </row>
+    <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="16"/>
+      <c r="D19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H20" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="I20" s="7" t="e">
+        <f>SUM(#REF!)</f>
+        <v>#REF!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H21" s="6"/>
+      <c r="I21" s="7"/>
+    </row>
+    <row r="22" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="F22" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G22" s="11"/>
+      <c r="H22" s="12" t="e">
+        <f>I16+I20</f>
+        <v>#REF!</v>
+      </c>
+      <c r="I22" s="10"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H23" s="6"/>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A26" s="8"/>
+      <c r="B26" s="8"/>
+      <c r="C26" s="8"/>
+      <c r="D26" s="8"/>
+      <c r="E26" s="8"/>
+      <c r="F26" s="8"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="8"/>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" s="9">
+        <f ca="1">TODAY()</f>
+        <v>45940</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="20"/>
-      <c r="G3" s="20"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="15"/>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="4">
-        <v>307698397</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-    </row>
-    <row r="6" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="11" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F6" s="16"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="15"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="15"/>
-      <c r="C7" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="4"/>
-    </row>
-    <row r="10" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A10" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="14"/>
-    </row>
-    <row r="11" spans="1:8" s="4" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B11" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
-      <c r="H12" s="9"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G13" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H13" s="10">
-        <f>SUM(H12:H12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G14" s="7"/>
-      <c r="H14" s="10"/>
-    </row>
-    <row r="15" spans="1:8" ht="18" x14ac:dyDescent="0.35">
-      <c r="A15" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-    </row>
-    <row r="16" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B16" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="22"/>
-      <c r="D16" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="9"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G18" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="H18" s="10">
-        <f>SUM(H17:H17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G19" s="7"/>
-      <c r="H19" s="10"/>
-    </row>
-    <row r="20" spans="1:8" ht="21" x14ac:dyDescent="0.4">
-      <c r="E20" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="23"/>
-      <c r="G20" s="24">
-        <f>H13+H18</f>
-        <v>0</v>
-      </c>
-      <c r="H20" s="25"/>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="G21" s="7"/>
-      <c r="H21" s="10"/>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B22" s="26"/>
-      <c r="C22" s="26"/>
-      <c r="D22" s="26"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="26"/>
-      <c r="G22" s="26"/>
-      <c r="H22" s="26"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="26"/>
-      <c r="D23" s="26"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="26"/>
-      <c r="G23" s="26"/>
-      <c r="H23" s="26"/>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="5"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="13">
-        <f ca="1">TODAY()</f>
-        <v>45882</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A28:C28"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="A22:H23"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A3:C3"/>
-    <mergeCell ref="E3:G3"/>
-    <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="F4:H4"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="F6:H6"/>
+  <mergeCells count="20">
+    <mergeCell ref="G3:I3"/>
+    <mergeCell ref="A2:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="G11:I12"/>
+    <mergeCell ref="A7:C7"/>
     <mergeCell ref="F7:H7"/>
-    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="G10:I10"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A12:B12"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C6" r:id="rId1" xr:uid="{93FC00EB-E059-4072-BAA3-1BAB22EB6ED9}"/>
+    <hyperlink ref="C10" r:id="rId1" xr:uid="{93FC00EB-E059-4072-BAA3-1BAB22EB6ED9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
--- a/data/minta_arajanlat.xlsx
+++ b/data/minta_arajanlat.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/595ecd328626fcde/csixwood program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="8_{BF28B8E6-6911-4314-842D-A6A0166F0E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84BB67D5-75F8-4367-969E-01FBD417C8AE}"/>
+  <xr:revisionPtr revIDLastSave="137" documentId="8_{BF28B8E6-6911-4314-842D-A6A0166F0E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C54B3227-F5AA-4AC8-927F-3B39A6371D8E}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{087A4F8E-2F22-482F-82DA-01AC2001CC58}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="29">
   <si>
     <t>Árajánlat</t>
   </si>
@@ -56,9 +56,6 @@
     <t>Adószám:</t>
   </si>
   <si>
-    <t>Sors.</t>
-  </si>
-  <si>
     <t>Megnevezés</t>
   </si>
   <si>
@@ -104,18 +101,12 @@
     <t>Bálint Bence ev.</t>
   </si>
   <si>
-    <t>Sezegd, Selmeci utca 17.</t>
-  </si>
-  <si>
     <t>91339968-1-26</t>
   </si>
   <si>
     <t>Típus, Szín</t>
   </si>
   <si>
-    <t>Munkadíj, gépkopoás, rezsi:</t>
-  </si>
-  <si>
     <t>Sz.</t>
   </si>
   <si>
@@ -123,6 +114,12 @@
   </si>
   <si>
     <t>Azonosító:</t>
+  </si>
+  <si>
+    <t>Szeged, Selmeci utca 17.</t>
+  </si>
+  <si>
+    <t>Munkadíj, gépkopás, rezsi:</t>
   </si>
 </sst>
 </file>
@@ -694,7 +691,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -732,58 +729,52 @@
     <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="42" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -856,9 +847,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>3</xdr:col>
-      <xdr:colOff>601343</xdr:colOff>
+      <xdr:colOff>962025</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>9526</xdr:rowOff>
+      <xdr:rowOff>261163</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -889,7 +880,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="123826"/>
-          <a:ext cx="2277743" cy="1047750"/>
+          <a:ext cx="2638425" cy="1213662"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1222,7 +1213,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1432CDCE-D980-42A2-8DB0-EED4DEC3C8EE}">
-  <dimension ref="A2:J30"/>
+  <dimension ref="A2:I31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3.28515625" style="2" customWidth="1"/>
@@ -1236,277 +1227,273 @@
     <col min="10" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="20"/>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="27" t="s">
+    <row r="2" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="27"/>
-      <c r="G2" s="27"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="27"/>
-    </row>
-    <row r="3" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="20"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="26" t="s">
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+    </row>
+    <row r="3" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="26"/>
+      <c r="D3" s="26"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+    </row>
+    <row r="4" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="26"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="27" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="27"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="26"/>
+    </row>
+    <row r="5" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="27" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="27"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+    </row>
+    <row r="6" spans="1:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="16"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+    </row>
+    <row r="7" spans="1:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
+      <c r="H7" s="13"/>
+      <c r="I7" s="13"/>
+    </row>
+    <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="F3" s="26"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-    </row>
-    <row r="4" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="24"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="28" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="28"/>
-      <c r="G4" s="29"/>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-      <c r="J4" s="22"/>
-    </row>
-    <row r="5" spans="1:10" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="25"/>
-      <c r="I5" s="25"/>
-    </row>
-    <row r="6" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="24"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="24"/>
-      <c r="F6" s="24"/>
-      <c r="G6" s="24"/>
-      <c r="H6" s="24"/>
-      <c r="I6" s="24"/>
-    </row>
-    <row r="7" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="21" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="F8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="21"/>
+      <c r="C9" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="21"/>
-      <c r="C7" s="21"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="21" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="22"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
+      <c r="F9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="2" t="s">
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
+      <c r="I9" s="23"/>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="3">
+        <v>307698397</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="21"/>
+      <c r="C11" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="25"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="21"/>
+      <c r="C12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>6</v>
+      </c>
+      <c r="B13" s="21"/>
+      <c r="C13" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="3">
-        <v>307698397</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-    </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="15"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="2" t="s">
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+    </row>
+    <row r="15" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="24" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="24"/>
+      <c r="C15" s="24"/>
+    </row>
+    <row r="16" spans="1:9" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" s="3"/>
-      <c r="B13" s="3"/>
-    </row>
-    <row r="14" spans="1:10" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="B14" s="13"/>
-      <c r="C14" s="13"/>
-    </row>
-    <row r="15" spans="1:10" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="16"/>
-      <c r="D15" s="1" t="s">
+      <c r="E16" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E15" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="1" t="s">
+      <c r="F16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="1"/>
+      <c r="H16" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1" t="s">
+      <c r="I16" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I15" s="1" t="s">
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H17" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="H16" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I16" s="7" t="e">
+      <c r="I17" s="7" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H17" s="6"/>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-    </row>
-    <row r="19" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="1" t="s">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H18" s="6"/>
+      <c r="I18" s="7"/>
+    </row>
+    <row r="19" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="C20" s="18"/>
+      <c r="D20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C19" s="16"/>
-      <c r="D19" s="1" t="s">
+      <c r="E20" s="1"/>
+      <c r="F20" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1" t="s">
+      <c r="G20" s="1"/>
+      <c r="H20" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1" t="s">
+      <c r="I20" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="I19" s="1" t="s">
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H21" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H20" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="I20" s="7" t="e">
+      <c r="I21" s="7" t="e">
         <f>SUM(#REF!)</f>
         <v>#REF!</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H21" s="6"/>
-      <c r="I21" s="7"/>
-    </row>
-    <row r="22" spans="1:9" ht="21" x14ac:dyDescent="0.25">
-      <c r="F22" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="12" t="e">
-        <f>I16+I20</f>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H22" s="6"/>
+      <c r="I22" s="7"/>
+    </row>
+    <row r="23" spans="1:9" ht="21" x14ac:dyDescent="0.25">
+      <c r="F23" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="11"/>
+      <c r="H23" s="12" t="e">
+        <f>I17+I21</f>
         <v>#REF!</v>
       </c>
-      <c r="I22" s="10"/>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H23" s="6"/>
-      <c r="I23" s="7"/>
-    </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="4"/>
-      <c r="I24" s="4"/>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A25" s="4"/>
+      <c r="I23" s="10"/>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H24" s="6"/>
+      <c r="I24" s="7"/>
+    </row>
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
       <c r="D25" s="4"/>
@@ -1517,61 +1504,72 @@
       <c r="I25" s="4"/>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="8"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="8"/>
-      <c r="H26" s="8"/>
-      <c r="I26" s="8"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="8"/>
+      <c r="B27" s="8"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="8"/>
+      <c r="E27" s="8"/>
+      <c r="F27" s="8"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="8"/>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C29" s="9">
+      <c r="C30" s="9">
         <f ca="1">TODAY()</f>
         <v>45940</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="G3:I3"/>
-    <mergeCell ref="A2:D3"/>
-    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A2:D4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:I5"/>
     <mergeCell ref="E2:I2"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="G11:I12"/>
-    <mergeCell ref="A7:C7"/>
-    <mergeCell ref="F7:H7"/>
-    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="G12:I13"/>
+    <mergeCell ref="A8:C8"/>
+    <mergeCell ref="F8:H8"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="A14:C14"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="G10:I10"/>
+    <mergeCell ref="G9:I9"/>
+    <mergeCell ref="A15:C15"/>
     <mergeCell ref="A11:B11"/>
+    <mergeCell ref="G11:I11"/>
     <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="C10" r:id="rId1" xr:uid="{93FC00EB-E059-4072-BAA3-1BAB22EB6ED9}"/>
+    <hyperlink ref="C11" r:id="rId1" xr:uid="{93FC00EB-E059-4072-BAA3-1BAB22EB6ED9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>

--- a/data/minta_arajanlat.xlsx
+++ b/data/minta_arajanlat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/595ecd328626fcde/csixwood program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="137" documentId="8_{BF28B8E6-6911-4314-842D-A6A0166F0E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C54B3227-F5AA-4AC8-927F-3B39A6371D8E}"/>
+  <xr:revisionPtr revIDLastSave="145" documentId="8_{BF28B8E6-6911-4314-842D-A6A0166F0E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E028566-DA25-4C55-A371-33A865F7BD17}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{087A4F8E-2F22-482F-82DA-01AC2001CC58}"/>
   </bookViews>
@@ -83,9 +83,6 @@
     <t>balintbence800@gmail.com</t>
   </si>
   <si>
-    <t>Az árak az ÁFA-t tartalmazzák. Az anyagról számlát tudok biztosítani, ha ez előre jelzésre kerül, munkadíjról még  nem.</t>
-  </si>
-  <si>
     <t>Ajánlat 14 napig érvényes. 14 nap leteltével újra tárgyalás szükséges</t>
   </si>
   <si>
@@ -120,6 +117,9 @@
   </si>
   <si>
     <t>Munkadíj, gépkopás, rezsi:</t>
+  </si>
+  <si>
+    <t>Az árak az ÁFA-t tartalmazzák.</t>
   </si>
 </sst>
 </file>
@@ -691,7 +691,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -744,24 +744,24 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -769,13 +769,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -890,10 +887,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1228,23 +1221,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="28" t="s">
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="26"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
@@ -1252,30 +1245,30 @@
       <c r="I3" s="14"/>
     </row>
     <row r="4" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="27" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4" s="27"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="26"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="19"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
     </row>
     <row r="5" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
-      <c r="E5" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="27"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
+      <c r="E5" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="19"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16"/>
@@ -1300,24 +1293,24 @@
       <c r="I7" s="13"/>
     </row>
     <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="F8" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="B9" s="23"/>
+      <c r="C9" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" s="20"/>
-      <c r="C8" s="20"/>
-      <c r="F8" s="20" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="20"/>
-      <c r="H8" s="20"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="21" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="21"/>
-      <c r="C9" s="2" t="s">
-        <v>21</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>2</v>
@@ -1327,25 +1320,25 @@
       <c r="I9" s="23"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="21"/>
+      <c r="B10" s="23"/>
       <c r="C10" s="3">
         <v>307698397</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
+      <c r="G10" s="26"/>
+      <c r="H10" s="26"/>
+      <c r="I10" s="26"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="21"/>
+      <c r="B11" s="23"/>
       <c r="C11" s="5" t="s">
         <v>15</v>
       </c>
@@ -1353,35 +1346,35 @@
         <v>14</v>
       </c>
       <c r="G11" s="25"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="21"/>
+      <c r="B12" s="23"/>
       <c r="C12" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="21"/>
+      <c r="B13" s="23"/>
       <c r="C13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="19"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
+        <v>21</v>
+      </c>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
@@ -1396,17 +1389,17 @@
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="21"/>
+      <c r="D16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B16" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="18"/>
-      <c r="D16" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="F16" s="17" t="s">
         <v>9</v>
@@ -1434,19 +1427,19 @@
     </row>
     <row r="19" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B19" s="10"/>
       <c r="C19" s="10"/>
     </row>
     <row r="20" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B20" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="18"/>
+      <c r="C20" s="21"/>
       <c r="D20" s="1" t="s">
         <v>8</v>
       </c>
@@ -1492,7 +1485,7 @@
     </row>
     <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1527,16 +1520,16 @@
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C30" s="9">
         <f ca="1">TODAY()</f>
-        <v>45940</v>
+        <v>45997</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1546,12 +1539,6 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="A2:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="E2:I2"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="G12:I13"/>
@@ -1566,6 +1553,12 @@
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A2:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="E2:I2"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>

--- a/data/minta_arajanlat.xlsx
+++ b/data/minta_arajanlat.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/595ecd328626fcde/csixwood program/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="145" documentId="8_{BF28B8E6-6911-4314-842D-A6A0166F0E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E028566-DA25-4C55-A371-33A865F7BD17}"/>
+  <xr:revisionPtr revIDLastSave="146" documentId="8_{BF28B8E6-6911-4314-842D-A6A0166F0E19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E37B149-B578-484F-942B-F3A97FB8C1EE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13140" xr2:uid="{087A4F8E-2F22-482F-82DA-01AC2001CC58}"/>
   </bookViews>
@@ -744,6 +744,27 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -752,27 +773,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="42" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1221,23 +1221,23 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:9" ht="28.5" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="20" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
-      <c r="I2" s="20"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
+      <c r="I2" s="27"/>
     </row>
     <row r="3" spans="1:9" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
       <c r="E3" s="14"/>
       <c r="F3" s="14"/>
       <c r="G3" s="14"/>
@@ -1245,30 +1245,30 @@
       <c r="I3" s="14"/>
     </row>
     <row r="4" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="19" t="s">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="25"/>
+      <c r="D4" s="25"/>
+      <c r="E4" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="19"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="25"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13"/>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
       <c r="D5" s="13"/>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="19"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="25"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" spans="1:9" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="16"/>
@@ -1293,108 +1293,108 @@
       <c r="I7" s="13"/>
     </row>
     <row r="8" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="F8" s="22" t="s">
+      <c r="B8" s="20"/>
+      <c r="C8" s="20"/>
+      <c r="F8" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="23"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
-      <c r="I9" s="23"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="21" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="23"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="3">
         <v>307698397</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G10" s="26"/>
-      <c r="H10" s="26"/>
-      <c r="I10" s="26"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="23"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="5" t="s">
         <v>15</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G11" s="25"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
+      <c r="A12" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="B12" s="23"/>
+      <c r="B12" s="21"/>
       <c r="C12" s="2" t="s">
         <v>26</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="23"/>
+      <c r="B13" s="21"/>
       <c r="C13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
     </row>
     <row r="15" spans="1:9" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="24" t="s">
+      <c r="A15" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="24"/>
-      <c r="C15" s="24"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="23"/>
     </row>
     <row r="16" spans="1:9" s="3" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="21"/>
+      <c r="C16" s="18"/>
       <c r="D16" s="1" t="s">
         <v>22</v>
       </c>
@@ -1436,10 +1436,10 @@
       <c r="A20" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="21"/>
+      <c r="C20" s="18"/>
       <c r="D20" s="1" t="s">
         <v>8</v>
       </c>
@@ -1473,10 +1473,7 @@
         <v>12</v>
       </c>
       <c r="G23" s="11"/>
-      <c r="H23" s="12" t="e">
-        <f>I17+I21</f>
-        <v>#REF!</v>
-      </c>
+      <c r="H23" s="12"/>
       <c r="I23" s="10"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -1529,7 +1526,7 @@
       </c>
       <c r="C30" s="9">
         <f ca="1">TODAY()</f>
-        <v>45997</v>
+        <v>46081</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
@@ -1539,6 +1536,12 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="G4:I4"/>
+    <mergeCell ref="A2:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:I5"/>
+    <mergeCell ref="E2:I2"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="G12:I13"/>
@@ -1553,12 +1556,6 @@
     <mergeCell ref="G11:I11"/>
     <mergeCell ref="A12:B12"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="G4:I4"/>
-    <mergeCell ref="A2:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:I5"/>
-    <mergeCell ref="E2:I2"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <hyperlinks>
